--- a/data/trans_orig/IP3109_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP3109_2023-Habitat-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>847</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>8489</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>11189</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13789</t>
+          <t>13668</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17524</t>
+          <t>17586</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9316</t>
+          <t>9315</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22272</t>
+          <t>22097</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19016</t>
+          <t>19754</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36410</t>
+          <t>35848</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17755</t>
+          <t>17519</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31491</t>
+          <t>31289</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16716</t>
+          <t>16827</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35791</t>
+          <t>34966</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37723</t>
+          <t>38052</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59683</t>
+          <t>60285</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63734</t>
+          <t>64154</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79897</t>
+          <t>79970</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77438</t>
+          <t>77070</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>102120</t>
+          <t>102404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>148435</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>177738</t>
+          <t>178946</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,67%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>397</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6598</t>
+          <t>6165</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>403</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13482</t>
+          <t>13271</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11922</t>
+          <t>11541</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25668</t>
+          <t>25252</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23078</t>
+          <t>23763</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21595</t>
+          <t>22289</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42839</t>
+          <t>42284</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35468</t>
+          <t>34891</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60801</t>
+          <t>60453</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28161</t>
+          <t>28839</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54834</t>
+          <t>53971</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>47861</t>
+          <t>47183</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75484</t>
+          <t>74674</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>82037</t>
+          <t>82025</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>118150</t>
+          <t>117142</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>106062</t>
+          <t>104638</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>131120</t>
+          <t>130369</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>133083</t>
+          <t>133573</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>163807</t>
+          <t>163878</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>246173</t>
+          <t>248139</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>286891</t>
+          <t>289009</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,65%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>10008</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5632</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>182</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>9309</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12704</t>
+          <t>13992</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>9996</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26866</t>
+          <t>27435</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13343</t>
+          <t>13049</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29952</t>
+          <t>29626</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>26161</t>
+          <t>26044</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>49460</t>
+          <t>50498</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18009</t>
+          <t>16986</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42257</t>
+          <t>42097</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29648</t>
+          <t>29318</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54121</t>
+          <t>54505</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54022</t>
+          <t>54370</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88607</t>
+          <t>89506</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>117145</t>
+          <t>118457</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>153017</t>
+          <t>155865</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>100356</t>
+          <t>102314</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>129006</t>
+          <t>129500</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>228275</t>
+          <t>226963</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>274463</t>
+          <t>278300</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>74,94%</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12775</t>
+          <t>12621</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>17122</t>
+          <t>18289</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22847</t>
+          <t>22588</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27016</t>
+          <t>26738</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>26252</t>
+          <t>26500</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>45249</t>
+          <t>45148</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19713</t>
+          <t>20102</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35888</t>
+          <t>35415</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17052</t>
+          <t>16924</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33015</t>
+          <t>32625</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41278</t>
+          <t>40421</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>63390</t>
+          <t>64561</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>107856</t>
+          <t>108001</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>127723</t>
+          <t>127190</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>115946</t>
+          <t>115336</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>136718</t>
+          <t>136323</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>228622</t>
+          <t>227700</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>257712</t>
+          <t>257691</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1641</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>11658</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17349</t>
+          <t>17643</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>924</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14238</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>30106</t>
+          <t>29990</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>30776</t>
+          <t>31954</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>32774</t>
+          <t>33161</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>55316</t>
+          <t>55632</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>48808</t>
+          <t>48949</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>75766</t>
+          <t>76236</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>69808</t>
+          <t>69128</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>102535</t>
+          <t>100865</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>126295</t>
+          <t>126640</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>166941</t>
+          <t>168418</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>100778</t>
+          <t>102273</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>140992</t>
+          <t>142856</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>126840</t>
+          <t>127036</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>174211</t>
+          <t>171494</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>239012</t>
+          <t>238246</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>300427</t>
+          <t>301551</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>417917</t>
+          <t>415547</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>470550</t>
+          <t>471396</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>453867</t>
+          <t>456600</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>508176</t>
+          <t>509139</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>890806</t>
+          <t>887092</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>967780</t>
+          <t>963706</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP3109_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP3109_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>873</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4295</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1630</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11040</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>9,02%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3076</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1215</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6808</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,0%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11189</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>7656</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13668</t>
+          <t>14450</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -1059,107 +1059,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13272</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8900</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>20044</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,84%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>16,38%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12060</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17586</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>12259</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7937</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>18596</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>10,41%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>6,74%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>15,8%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>25531</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>18424</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>33928</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>10,63%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,85%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>15084</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9315</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>22097</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>6,84%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>16,22%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>27144</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>19754</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>35848</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>10,87%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24873</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16830</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>33883</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>27,69%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>23681</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17519</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31289</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>20,88%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>27,58%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>24844</t>
+          <t>25045</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16827</t>
+          <t>17802</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34966</t>
+          <t>33354</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>48525</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38052</t>
+          <t>39534</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60285</t>
+          <t>62035</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>78607</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>69204</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89945</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>64,23%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>56,55%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>73,49%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>72627</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>64154</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>79970</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>64,03%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>56,56%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>70,5%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90310</t>
+          <t>75227</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77070</t>
+          <t>66225</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>102404</t>
+          <t>83627</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>162938</t>
+          <t>153834</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>148435</t>
+          <t>140700</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>178946</t>
+          <t>167075</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>69,58%</t>
         </is>
       </c>
     </row>
@@ -1398,74 +1398,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>122384</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>122384</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>122384</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>113426</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>113426</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>113426</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>117724</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>117724</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>117724</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>136250</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>136250</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>136250</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>350</t>
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>249677</t>
+          <t>240108</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>249677</t>
+          <t>240108</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>249677</t>
+          <t>240108</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2138</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6165</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>451</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,22 +1590,22 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>364</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -1628,107 +1628,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2807</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2896</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>3397</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>3270</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3482</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12599</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>9772</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5523</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>16175</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,69%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13271</t>
+          <t>15173</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17590</t>
+          <t>15909</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25252</t>
+          <t>23477</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25668</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18238</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>34794</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15,05%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>15902</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>10917</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>23763</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,54%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5,87%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12,77%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30718</t>
+          <t>15910</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22289</t>
+          <t>10461</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42284</t>
+          <t>23691</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>46620</t>
+          <t>41578</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34891</t>
+          <t>32149</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60453</t>
+          <t>53562</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>56624</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>45070</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>70161</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>24,49%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>19,49%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>30,34%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>38503</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>28839</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>53971</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>20,69%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>15,5%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>29,0%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59804</t>
+          <t>34848</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>47183</t>
+          <t>26517</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>74674</t>
+          <t>44622</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>98307</t>
+          <t>91472</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>82025</t>
+          <t>76658</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>117142</t>
+          <t>109043</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -2080,72 +2080,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>141978</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>127977</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>154662</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>61,4%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>55,34%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>66,88%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>119255</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>104638</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>130369</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>64,08%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>56,22%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>70,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>149181</t>
+          <t>118038</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>133573</t>
+          <t>106275</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>163878</t>
+          <t>128758</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>268436</t>
+          <t>260015</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>248139</t>
+          <t>241801</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>289009</t>
+          <t>278667</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>67,66%</t>
         </is>
       </c>
     </row>
@@ -2193,74 +2193,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>180593</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>180593</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>180593</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>247520</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>247520</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>247520</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>593</t>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3695</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>9595</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3955</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4449</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3313</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>943</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>9051</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10008</t>
+          <t>12317</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>744</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2602</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>786</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6834</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>4471</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1652</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9309</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13992</t>
+          <t>12770</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -2649,72 +2649,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>15614</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>10085</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>23186</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>13,92%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>17795</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>9996</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>27435</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>14,57%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>17584</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>11952</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29626</t>
+          <t>25380</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>37668</t>
+          <t>33198</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>26044</t>
+          <t>25468</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>50498</t>
+          <t>42886</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -2762,72 +2762,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>37852</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>28033</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>50225</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>22,73%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>16,83%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>30,16%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>30881</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>16986</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>42097</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>16,4%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>9,02%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>22,36%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>40106</t>
+          <t>30399</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29318</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54505</t>
+          <t>39401</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>70987</t>
+          <t>68252</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54370</t>
+          <t>55658</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89506</t>
+          <t>83820</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>132807</t>
+          <t>105443</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118457</t>
+          <t>92606</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>155865</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>115963</t>
+          <t>100307</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>102314</t>
+          <t>90214</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>129500</t>
+          <t>109185</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>248771</t>
+          <t>205750</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>226963</t>
+          <t>189159</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>278300</t>
+          <t>221253</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>68,81%</t>
         </is>
       </c>
     </row>
@@ -2988,74 +2988,74 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>155038</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>155038</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>155038</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>183089</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>183089</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>183089</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>443</t>
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3105,107 +3105,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>2557</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>3051</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -3331,72 +3331,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>6045</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>3033</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>10796</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>3772</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>8360</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3525</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12621</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>10427</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>18289</t>
+          <t>16617</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -3444,72 +3444,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>17873</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>12196</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>25872</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>10,76%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>15,57%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>15813</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>10003</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>22588</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>13,73%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>18824</t>
+          <t>15964</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12481</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>26738</t>
+          <t>22920</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>34637</t>
+          <t>33837</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>26500</t>
+          <t>25101</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>45148</t>
+          <t>43537</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -3557,72 +3557,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>23269</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>16408</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>31054</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>14,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>18,69%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>27484</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>20102</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>35415</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>16,71%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>12,22%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>21,53%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>24243</t>
+          <t>27184</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16924</t>
+          <t>20665</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32625</t>
+          <t>36441</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>50453</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>40421</t>
+          <t>39469</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>64561</t>
+          <t>61901</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -3670,72 +3670,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>118504</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>108046</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>126999</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>71,32%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>65,02%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>76,43%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>117449</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>108001</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>127190</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>71,39%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>65,65%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>77,31%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>126724</t>
+          <t>116450</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>115336</t>
+          <t>106174</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>136323</t>
+          <t>125992</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>244173</t>
+          <t>234953</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>227700</t>
+          <t>221504</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>257691</t>
+          <t>249306</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,51%</t>
         </is>
       </c>
     </row>
@@ -3783,74 +3783,74 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>163979</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>163979</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>163979</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>177309</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>177309</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>177309</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>467</t>
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1641</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>11839</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11658</t>
+          <t>11956</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17643</t>
+          <t>18335</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -4013,107 +4013,107 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>5763</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>2070</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>6299</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5589</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>3343</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>1090</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>7580</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>1087</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>6323</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>3157</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>924</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>7825</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>21091</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>29990</t>
+          <t>29590</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>22083</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>31954</t>
+          <t>30160</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>43175</t>
+          <t>40784</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>33161</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>55632</t>
+          <t>52624</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -4239,72 +4239,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>72427</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>58950</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>85228</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>10,55%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>12,42%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>61570</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>48949</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>76236</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>9,44%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>11,69%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>84499</t>
+          <t>61717</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>69128</t>
+          <t>49652</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>100865</t>
+          <t>75427</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>146069</t>
+          <t>134144</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>126640</t>
+          <t>117723</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>168418</t>
+          <t>154260</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -4352,72 +4352,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>142618</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>123591</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>162800</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>20,78%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>18,01%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>23,72%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>120549</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>102273</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>142856</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>18,48%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>15,68%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>21,9%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>148997</t>
+          <t>117477</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>127036</t>
+          <t>101871</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>171494</t>
+          <t>135764</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>269546</t>
+          <t>260095</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>238246</t>
+          <t>237508</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>301551</t>
+          <t>290234</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -4465,72 +4465,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>444531</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>422107</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>466943</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>64,77%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>61,5%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>68,04%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>442139</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>415547</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>471396</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>67,78%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>63,7%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>72,27%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>482179</t>
+          <t>410022</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>456600</t>
+          <t>387816</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>509139</t>
+          <t>429729</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>924319</t>
+          <t>854553</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>887092</t>
+          <t>823894</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>963706</t>
+          <t>882122</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>67,67%</t>
         </is>
       </c>
     </row>
@@ -4578,74 +4578,74 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>652309</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>652309</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>652309</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>617334</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>617334</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>617334</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>744169</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>744169</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>744169</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>1853</t>
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1396478</t>
+          <t>1303646</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1396478</t>
+          <t>1303646</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1396478</t>
+          <t>1303646</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
